--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -413,736 +413,991 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.17755</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.05505</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.06286</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.03465</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05154</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.89173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.16107</v>
+        <v>17.14408</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03218</v>
+        <v>16.71333</v>
       </c>
       <c r="E3" t="n">
-        <v>17.14538</v>
+        <v>17.03234</v>
       </c>
       <c r="F3" t="n">
-        <v>42.87388</v>
+        <v>43.56261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05133</v>
+        <v>0.05224</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86396</v>
+        <v>1.90295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.31427</v>
+        <v>17.63844</v>
       </c>
       <c r="D4" t="n">
-        <v>17.02225</v>
+        <v>16.84866</v>
       </c>
       <c r="E4" t="n">
-        <v>17.3973</v>
+        <v>17.16947</v>
       </c>
       <c r="F4" t="n">
-        <v>44.13535</v>
+        <v>43.90531</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05204</v>
+        <v>0.05276</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89018</v>
+        <v>1.87617</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.42218</v>
+        <v>17.40806</v>
       </c>
       <c r="D5" t="n">
-        <v>16.9238</v>
+        <v>17.0354</v>
       </c>
       <c r="E5" t="n">
-        <v>16.93727</v>
+        <v>17.16359</v>
       </c>
       <c r="F5" t="n">
-        <v>43.41814</v>
+        <v>44.31417</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05323</v>
+        <v>0.05256</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87641</v>
+        <v>1.86983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.78011</v>
+        <v>17.32467</v>
       </c>
       <c r="D6" t="n">
-        <v>16.98438</v>
+        <v>16.81723</v>
       </c>
       <c r="E6" t="n">
-        <v>17.18836</v>
+        <v>17.26404</v>
       </c>
       <c r="F6" t="n">
-        <v>43.98917</v>
+        <v>44.38186</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05219</v>
+        <v>0.05293</v>
       </c>
       <c r="H6" t="n">
-        <v>1.90124</v>
+        <v>1.87756</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.25468</v>
+        <v>17.46077</v>
       </c>
       <c r="D7" t="n">
-        <v>17.16193</v>
+        <v>17.1486</v>
       </c>
       <c r="E7" t="n">
-        <v>17.18032</v>
+        <v>17.36163</v>
       </c>
       <c r="F7" t="n">
-        <v>44.02822</v>
+        <v>43.12956</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05222</v>
+        <v>0.05256</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89395</v>
+        <v>1.8659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.20957</v>
+        <v>17.31923</v>
       </c>
       <c r="D8" t="n">
-        <v>16.81349</v>
+        <v>17.28959</v>
       </c>
       <c r="E8" t="n">
-        <v>17.4428</v>
+        <v>17.29414</v>
       </c>
       <c r="F8" t="n">
-        <v>43.8447</v>
+        <v>43.62362</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05066</v>
+        <v>0.05254</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84589</v>
+        <v>1.89728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.27682</v>
+        <v>17.12563</v>
       </c>
       <c r="D9" t="n">
-        <v>16.89389</v>
+        <v>16.86352</v>
       </c>
       <c r="E9" t="n">
-        <v>17.08895</v>
+        <v>17.11774</v>
       </c>
       <c r="F9" t="n">
-        <v>43.6574</v>
+        <v>43.90595</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05224</v>
+        <v>0.05221</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88778</v>
+        <v>1.89037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.00757</v>
+        <v>17.33662</v>
       </c>
       <c r="D10" t="n">
-        <v>16.93824</v>
+        <v>17.16008</v>
       </c>
       <c r="E10" t="n">
-        <v>17.02408</v>
+        <v>17.27767</v>
       </c>
       <c r="F10" t="n">
-        <v>44.339</v>
+        <v>44.05952</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05257</v>
+        <v>0.05171</v>
       </c>
       <c r="H10" t="n">
-        <v>1.90257</v>
+        <v>1.85635</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>17.53499</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17.10185</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.30889</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.85159</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05273</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.84695</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.3546</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.68409</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.147</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.63148</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.63835</v>
+        <v>17.40429</v>
       </c>
       <c r="D13" t="n">
-        <v>1.17401</v>
+        <v>17.07962</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.3149</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.65457</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05257</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.87521</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.63263</v>
+        <v>17.37204</v>
       </c>
       <c r="D14" t="n">
-        <v>1.14938</v>
+        <v>17.11869</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.19204</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.94357</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05222</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.84257</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.646</v>
+        <v>17.28672</v>
       </c>
       <c r="D15" t="n">
-        <v>1.16997</v>
+        <v>16.47476</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.19218</v>
+      </c>
+      <c r="F15" t="n">
+        <v>44.06038</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.90796</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.63178</v>
+        <v>17.35009</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1539</v>
+        <v>17.08242</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.19155</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.76216</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05257</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.87274</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61756</v>
+        <v>17.2206</v>
       </c>
       <c r="D17" t="n">
-        <v>1.15285</v>
+        <v>17.13446</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.21461</v>
+      </c>
+      <c r="F17" t="n">
+        <v>44.32363</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.62195</v>
+        <v>17.22184</v>
       </c>
       <c r="D18" t="n">
-        <v>1.16133</v>
+        <v>17.02736</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.10306</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.93676</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.87999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.62226</v>
+        <v>17.60136</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1639</v>
+        <v>17.10268</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.30182</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.47735</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.85827</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.63605</v>
+        <v>17.35165</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1424</v>
+        <v>16.91737</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.99774</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.26612</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.89916</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.61489</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.16091</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.62683</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.15765</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.77713</v>
+        <v>0.62914</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08227</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.63298</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.98295</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11194</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.007860000000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09506000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13212</v>
+        <v>1.12015</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7714</v>
+        <v>0.6202</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08303000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.62061</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.99073</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11129</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.007849999999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09599000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1313</v>
+        <v>1.14752</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.76425</v>
+        <v>0.63454</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08409999999999999</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.62762</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.98685</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.10982</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00793</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09603</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12593</v>
+        <v>1.13323</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.78215</v>
+        <v>0.62261</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08391999999999999</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.6206700000000001</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.00187</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11416</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09608999999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12999</v>
+        <v>1.16953</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.76917</v>
+        <v>0.63423</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08434999999999999</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.62401</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.99304</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10979</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09539</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12994</v>
+        <v>1.13726</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76256</v>
+        <v>0.62072</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.6351</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.98613</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11315</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.008030000000000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09396</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13</v>
+        <v>1.15396</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75674</v>
+        <v>0.62964</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08260000000000001</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.61476</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.98943</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11256</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09379999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.13089</v>
+        <v>1.15067</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.62575</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.13944</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.78445</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08441</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.62108</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.99683</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11199</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09657</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13042</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7904099999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08197</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.63017</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11145</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09582</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.13103</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.77471</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08257</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.62727</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9746899999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11166</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09631000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.13087</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.77484</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08379</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.63076</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.00257</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11395</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12782</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.74964</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08414000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.62708</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.01308</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11292</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09709</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12771</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.76102</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08329</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6282</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.99605</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11102</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12912</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.78404</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08273</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.64238</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.98378</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11183</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.13159</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.78329</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.08495</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.60615</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.97357</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11288</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09501</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13148</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="C39" t="n">
+        <v>0.78224</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08297</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.61681</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.99188</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11458</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09827</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13045</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>0.77251</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08172</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.63028</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.00181</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.11009</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00784</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09864000000000001</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.13416</v>
+      <c r="C40" t="n">
+        <v>0.76162</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08326</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.62654</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.99877</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11439</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09558999999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12844</v>
       </c>
     </row>
   </sheetData>
